--- a/output/pdf_financials_xlsx/VGN.xlsx
+++ b/output/pdf_financials_xlsx/VGN.xlsx
@@ -4533,40 +4533,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.870559</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.661775</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.332813</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.204858</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.356656</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.373185</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.416646</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.782195</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.784734</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.784734</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.99458</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.99458</v>
       </c>
     </row>
     <row r="93">
@@ -8104,7 +8104,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n">
         <v>1.870559</v>
       </c>

--- a/output/pdf_financials_xlsx/VGN.xlsx
+++ b/output/pdf_financials_xlsx/VGN.xlsx
@@ -19398,7 +19398,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -23094,7 +23094,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -24736,7 +24736,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">

--- a/output/pdf_financials_xlsx/VGN.xlsx
+++ b/output/pdf_financials_xlsx/VGN.xlsx
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.785384</v>
+        <v>-0.756262</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-0.97881</v>
+        <v>-0.959632</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-1.052775</v>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.029122</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.019178</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.878098</v>
+        <v>-0.848976</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.009442</v>
+        <v>-0.990264</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.079906</v>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.87729</v>
+        <v>-0.848168</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.009442</v>
+        <v>-0.990264</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.035327</v>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-3.850781871890959</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.99847441519249</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -3412,40 +3412,40 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.077433</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.044474</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.048869</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.027972</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.052685</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.033448</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.029627</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.034456</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.030865</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.025708</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.054675</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.063252</v>
       </c>
     </row>
     <row r="68">
@@ -3553,16 +3553,16 @@
         <v>0</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.027388</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>0.034419</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>0.043262</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>0.025356</v>
       </c>
       <c r="J70" s="3" t="n">
         <v>0</v>
@@ -3596,16 +3596,16 @@
         <v>0</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>0.027388</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>0.034419</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.174358</v>
+        <v>0.21762</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>0.025356</v>
       </c>
       <c r="J71" s="3" t="n">
         <v>0</v>
@@ -3768,16 +3768,16 @@
         <v>0.344</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.114188</v>
+        <v>0.0868</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.034419</v>
+        <v>0</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.043262</v>
+        <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.025356</v>
+        <v>0</v>
       </c>
       <c r="J75" s="3" t="n">
         <v>0</v>
@@ -4005,18 +4005,16 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.02005082419533709</v>
+        <v>0.02538037876265521</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.01506087561147769</v>
+        <v>0.02261523698821117</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.02648004652288874</v>
-      </c>
-      <c r="I80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.03221611928994786</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>0.002222131468925653</v>
       </c>
       <c r="J80" s="1" t="inlineStr">
         <is>
@@ -5713,13 +5711,13 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-0.333929</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-0.21814</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0</v>
+        <v>-1.25858</v>
       </c>
       <c r="E114" s="1" t="inlineStr">
         <is>
@@ -5774,13 +5772,13 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>4.064469</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.22352</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.730663</v>
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
@@ -6140,13 +6138,13 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>0</v>
+        <v>-0.096081</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-0.087765</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-0.139095</v>
       </c>
       <c r="E121" s="1" t="inlineStr">
         <is>
@@ -12010,7 +12008,11 @@
           <t>Lease liabilities (Note 13)</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -13412,7 +13414,11 @@
           <t>Lease liabilities (Note 16)</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -16352,7 +16358,11 @@
           <t>Share repurchase</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -16580,7 +16590,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E131" s="5" t="n">
         <v>4.064469</v>
       </c>
@@ -16652,7 +16666,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E132" s="5" t="n">
         <v>-0.333929</v>
       </c>
@@ -17706,7 +17724,11 @@
           <t>Share repurchase</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E146" s="5" t="n">
         <v>-0.096081</v>
       </c>
@@ -26242,7 +26264,11 @@
           <t>Income tax recovery (Note 21)</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -27974,7 +28000,11 @@
           <t>Income tax recovery (Note 19)</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E284" s="5" t="n">
         <v>0.029122</v>
       </c>
